--- a/static/static_MP_EcoEquivalencyFactors.xlsx
+++ b/static/static_MP_EcoEquivalencyFactors.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\55586\Desktop\tools\access tool\access-tool-migration\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{88A2E867-6505-4E33-95FA-B76042C0C39A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73F27EAB-7F46-4457-B622-5F1442F31D6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8700" yWindow="3255" windowWidth="23070" windowHeight="14910" xr2:uid="{E773620C-AD12-4A13-8F9C-76102836CE47}"/>
+    <workbookView xWindow="13725" yWindow="3165" windowWidth="23070" windowHeight="14910" xr2:uid="{E773620C-AD12-4A13-8F9C-76102836CE47}"/>
   </bookViews>
   <sheets>
     <sheet name="static" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">static!$A$1:$H$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3473" uniqueCount="87">
   <si>
     <t/>
   </si>
@@ -128,9 +131,6 @@
     <t>Arsenic Compounds</t>
   </si>
   <si>
-    <t>Arsenic compounds</t>
-  </si>
-  <si>
     <t>Hg - No EcoEF</t>
   </si>
   <si>
@@ -150,9 +150,6 @@
   </si>
   <si>
     <t>Cadmium</t>
-  </si>
-  <si>
-    <t>Cadmium compounds</t>
   </si>
   <si>
     <t>Chlorinated Dibenzodioxins and Furans as 2,3,7,8-Tetrachlorodibenzo-p-dioxin</t>
@@ -732,36 +729,36 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>4</v>
@@ -784,10 +781,10 @@
     </row>
     <row r="3" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>4</v>
@@ -810,10 +807,10 @@
     </row>
     <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>4</v>
@@ -836,10 +833,10 @@
     </row>
     <row r="5" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>4</v>
@@ -862,10 +859,10 @@
     </row>
     <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>4</v>
@@ -888,10 +885,10 @@
     </row>
     <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>4</v>
@@ -914,10 +911,10 @@
     </row>
     <row r="8" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>4</v>
@@ -940,10 +937,10 @@
     </row>
     <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>4</v>
@@ -966,10 +963,10 @@
     </row>
     <row r="10" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>4</v>
@@ -992,10 +989,10 @@
     </row>
     <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>4</v>
@@ -1018,10 +1015,10 @@
     </row>
     <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>4</v>
@@ -1044,10 +1041,10 @@
     </row>
     <row r="13" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>4</v>
@@ -1070,10 +1067,10 @@
     </row>
     <row r="14" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>4</v>
@@ -1096,10 +1093,10 @@
     </row>
     <row r="15" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>4</v>
@@ -1122,19 +1119,19 @@
     </row>
     <row r="16" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F16" s="3">
         <v>2.6707029701718001E-5</v>
@@ -1148,19 +1145,19 @@
     </row>
     <row r="17" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F17" s="3">
         <v>1.00368385318728E-5</v>
@@ -1174,19 +1171,19 @@
     </row>
     <row r="18" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F18" s="3">
         <v>1.25309052188713E-3</v>
@@ -1200,19 +1197,19 @@
     </row>
     <row r="19" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F19" s="3">
         <v>1.31023088523158E-3</v>
@@ -1226,19 +1223,19 @@
     </row>
     <row r="20" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F20" s="3">
         <v>1.9681894894452E-3</v>
@@ -1252,19 +1249,19 @@
     </row>
     <row r="21" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F21" s="3">
         <v>0.102531315930583</v>
@@ -1278,19 +1275,19 @@
     </row>
     <row r="22" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F22" s="3">
         <v>3.01733561003232E-2</v>
@@ -1304,19 +1301,19 @@
     </row>
     <row r="23" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F23" s="3">
         <v>1.32669933933788E-2</v>
@@ -1330,19 +1327,19 @@
     </row>
     <row r="24" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3">
         <v>4.4342927309782801E-2</v>
@@ -1356,19 +1353,19 @@
     </row>
     <row r="25" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F25" s="3">
         <v>0.132810577772737</v>
@@ -1382,19 +1379,19 @@
     </row>
     <row r="26" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F26" s="3">
         <v>4.6690302161022601E-2</v>
@@ -1408,19 +1405,19 @@
     </row>
     <row r="27" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F27" s="3">
         <v>3.5035702182728201</v>
@@ -1434,19 +1431,19 @@
     </row>
     <row r="28" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F28" s="3">
         <v>2.56632300584398E-2</v>
@@ -1460,19 +1457,19 @@
     </row>
     <row r="29" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F29" s="3">
         <v>4.2325594216692297E-2</v>
@@ -1486,19 +1483,19 @@
     </row>
     <row r="30" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F30" s="3">
         <v>0.22628202326574201</v>
@@ -1512,19 +1509,19 @@
     </row>
     <row r="31" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F31" s="3">
         <v>1</v>
@@ -1538,19 +1535,19 @@
     </row>
     <row r="32" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F32" s="3">
         <v>7.5976281018958994E-2</v>
@@ -1564,25 +1561,25 @@
     </row>
     <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F33" s="3">
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>0</v>
@@ -1590,25 +1587,25 @@
     </row>
     <row r="34" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F34" s="3">
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>0</v>
@@ -1616,25 +1613,25 @@
     </row>
     <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F35" s="3">
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>0</v>
@@ -1642,10 +1639,10 @@
     </row>
     <row r="36" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>29</v>
@@ -1668,7 +1665,7 @@
     </row>
     <row r="37" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>25</v>
@@ -1694,7 +1691,7 @@
     </row>
     <row r="38" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>24</v>
@@ -1720,7 +1717,7 @@
     </row>
     <row r="39" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>23</v>
@@ -1746,7 +1743,7 @@
     </row>
     <row r="40" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>22</v>
@@ -1772,7 +1769,7 @@
     </row>
     <row r="41" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>21</v>
@@ -1798,7 +1795,7 @@
     </row>
     <row r="42" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>20</v>
@@ -1824,7 +1821,7 @@
     </row>
     <row r="43" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>19</v>
@@ -1850,7 +1847,7 @@
     </row>
     <row r="44" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>18</v>
@@ -1876,7 +1873,7 @@
     </row>
     <row r="45" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>17</v>
@@ -1902,7 +1899,7 @@
     </row>
     <row r="46" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
@@ -1928,7 +1925,7 @@
     </row>
     <row r="47" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -1954,7 +1951,7 @@
     </row>
     <row r="48" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>14</v>
@@ -1980,7 +1977,7 @@
     </row>
     <row r="49" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>13</v>
@@ -2006,7 +2003,7 @@
     </row>
     <row r="50" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>12</v>
@@ -2032,7 +2029,7 @@
     </row>
     <row r="51" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>11</v>
@@ -2058,7 +2055,7 @@
     </row>
     <row r="52" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>10</v>
@@ -2084,7 +2081,7 @@
     </row>
     <row r="53" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>9</v>
@@ -2110,7 +2107,7 @@
     </row>
     <row r="54" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>8</v>
@@ -2136,7 +2133,7 @@
     </row>
     <row r="55" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>7</v>
@@ -2162,7 +2159,7 @@
     </row>
     <row r="56" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>5</v>
@@ -2188,10 +2185,10 @@
     </row>
     <row r="57" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>4</v>
@@ -2214,10 +2211,10 @@
     </row>
     <row r="58" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>4</v>
@@ -2240,10 +2237,10 @@
     </row>
     <row r="59" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>4</v>
@@ -2266,10 +2263,10 @@
     </row>
     <row r="60" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>4</v>
@@ -2292,10 +2289,10 @@
     </row>
     <row r="61" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>4</v>
@@ -2318,10 +2315,10 @@
     </row>
     <row r="62" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>4</v>
@@ -2344,10 +2341,10 @@
     </row>
     <row r="63" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>4</v>
@@ -2370,10 +2367,10 @@
     </row>
     <row r="64" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>4</v>
@@ -2396,10 +2393,10 @@
     </row>
     <row r="65" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>4</v>
@@ -2422,10 +2419,10 @@
     </row>
     <row r="66" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>4</v>
@@ -2448,10 +2445,10 @@
     </row>
     <row r="67" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>4</v>
@@ -2474,10 +2471,10 @@
     </row>
     <row r="68" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>4</v>
@@ -2500,10 +2497,10 @@
     </row>
     <row r="69" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>4</v>
@@ -2526,10 +2523,10 @@
     </row>
     <row r="70" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>4</v>
@@ -2552,19 +2549,19 @@
     </row>
     <row r="71" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F71" s="3">
         <v>1.00082370337604E-4</v>
@@ -2578,19 +2575,19 @@
     </row>
     <row r="72" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F72" s="3">
         <v>3.7506301006279502E-5</v>
@@ -2604,19 +2601,19 @@
     </row>
     <row r="73" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F73" s="3">
         <v>3.1189216393290899E-2</v>
@@ -2630,19 +2627,19 @@
     </row>
     <row r="74" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F74" s="3">
         <v>1.6312338194513301E-3</v>
@@ -2656,19 +2653,19 @@
     </row>
     <row r="75" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3">
         <v>2.3115044886036899E-3</v>
@@ -2682,19 +2679,19 @@
     </row>
     <row r="76" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F76" s="3">
         <v>0.22104760680178101</v>
@@ -2708,19 +2705,19 @@
     </row>
     <row r="77" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F77" s="3">
         <v>3.2261017399926199E-2</v>
@@ -2734,19 +2731,19 @@
     </row>
     <row r="78" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F78" s="3">
         <v>0.14267289719429799</v>
@@ -2760,19 +2757,19 @@
     </row>
     <row r="79" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F79" s="3">
         <v>4.7732153168308401E-2</v>
@@ -2786,19 +2783,19 @@
     </row>
     <row r="80" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F80" s="3">
         <v>0.142906747390462</v>
@@ -2812,19 +2809,19 @@
     </row>
     <row r="81" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F81" s="3">
         <v>5.0580373628807802E-2</v>
@@ -2838,19 +2835,19 @@
     </row>
     <row r="82" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F82" s="3">
         <v>3.4677644557586</v>
@@ -2864,19 +2861,19 @@
     </row>
     <row r="83" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F83" s="3">
         <v>7.5552023068697601E-3</v>
@@ -2890,19 +2887,19 @@
     </row>
     <row r="84" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F84" s="3">
         <v>4.6095537272986403E-2</v>
@@ -2916,19 +2913,19 @@
     </row>
     <row r="85" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F85" s="3">
         <v>6.7179621362434494E-2</v>
@@ -2942,19 +2939,19 @@
     </row>
     <row r="86" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F86" s="3">
         <v>1</v>
@@ -2968,19 +2965,19 @@
     </row>
     <row r="87" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F87" s="3">
         <v>6.9872014171500803E-3</v>
@@ -2994,25 +2991,25 @@
     </row>
     <row r="88" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C88" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D88" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E88" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F88" s="3">
         <v>1</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>0</v>
@@ -3020,25 +3017,25 @@
     </row>
     <row r="89" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B89" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C89" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E89" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F89" s="3">
         <v>1</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>0</v>
@@ -3046,25 +3043,25 @@
     </row>
     <row r="90" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F90" s="3">
         <v>1</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>0</v>
@@ -3072,10 +3069,10 @@
     </row>
     <row r="91" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>29</v>
@@ -3098,7 +3095,7 @@
     </row>
     <row r="92" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>25</v>
@@ -3124,7 +3121,7 @@
     </row>
     <row r="93" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>24</v>
@@ -3150,7 +3147,7 @@
     </row>
     <row r="94" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>23</v>
@@ -3176,7 +3173,7 @@
     </row>
     <row r="95" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>22</v>
@@ -3202,7 +3199,7 @@
     </row>
     <row r="96" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>21</v>
@@ -3228,7 +3225,7 @@
     </row>
     <row r="97" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>20</v>
@@ -3254,7 +3251,7 @@
     </row>
     <row r="98" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>19</v>
@@ -3280,7 +3277,7 @@
     </row>
     <row r="99" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>18</v>
@@ -3306,7 +3303,7 @@
     </row>
     <row r="100" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>17</v>
@@ -3332,7 +3329,7 @@
     </row>
     <row r="101" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>16</v>
@@ -3358,7 +3355,7 @@
     </row>
     <row r="102" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>15</v>
@@ -3384,7 +3381,7 @@
     </row>
     <row r="103" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>14</v>
@@ -3410,7 +3407,7 @@
     </row>
     <row r="104" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>13</v>
@@ -3436,7 +3433,7 @@
     </row>
     <row r="105" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>12</v>
@@ -3462,7 +3459,7 @@
     </row>
     <row r="106" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>11</v>
@@ -3488,7 +3485,7 @@
     </row>
     <row r="107" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>10</v>
@@ -3514,7 +3511,7 @@
     </row>
     <row r="108" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>9</v>
@@ -3540,7 +3537,7 @@
     </row>
     <row r="109" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>8</v>
@@ -3566,7 +3563,7 @@
     </row>
     <row r="110" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>7</v>
@@ -3592,7 +3589,7 @@
     </row>
     <row r="111" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>5</v>
@@ -3618,10 +3615,10 @@
     </row>
     <row r="112" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>4</v>
@@ -3644,10 +3641,10 @@
     </row>
     <row r="113" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>4</v>
@@ -3670,10 +3667,10 @@
     </row>
     <row r="114" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>4</v>
@@ -3696,10 +3693,10 @@
     </row>
     <row r="115" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>4</v>
@@ -3722,10 +3719,10 @@
     </row>
     <row r="116" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>4</v>
@@ -3748,10 +3745,10 @@
     </row>
     <row r="117" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>4</v>
@@ -3774,10 +3771,10 @@
     </row>
     <row r="118" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>4</v>
@@ -3800,10 +3797,10 @@
     </row>
     <row r="119" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>4</v>
@@ -3826,10 +3823,10 @@
     </row>
     <row r="120" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>4</v>
@@ -3852,10 +3849,10 @@
     </row>
     <row r="121" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>4</v>
@@ -3878,10 +3875,10 @@
     </row>
     <row r="122" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>4</v>
@@ -3904,10 +3901,10 @@
     </row>
     <row r="123" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>4</v>
@@ -3930,10 +3927,10 @@
     </row>
     <row r="124" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>4</v>
@@ -3956,10 +3953,10 @@
     </row>
     <row r="125" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>4</v>
@@ -3982,19 +3979,19 @@
     </row>
     <row r="126" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F126" s="3">
         <v>3.5055598511979803E-4</v>
@@ -4008,19 +4005,19 @@
     </row>
     <row r="127" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F127" s="3">
         <v>1.8860259900830201E-4</v>
@@ -4034,19 +4031,19 @@
     </row>
     <row r="128" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F128" s="3">
         <v>1.16513878026817E-2</v>
@@ -4060,19 +4057,19 @@
     </row>
     <row r="129" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F129" s="3">
         <v>1.09229763708434E-2</v>
@@ -4086,19 +4083,19 @@
     </row>
     <row r="130" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F130" s="3">
         <v>5.7491599472917401E-3</v>
@@ -4112,19 +4109,19 @@
     </row>
     <row r="131" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F131" s="3">
         <v>2.7241458114203199</v>
@@ -4138,19 +4135,19 @@
     </row>
     <row r="132" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F132" s="3">
         <v>5.4075311208433903E-2</v>
@@ -4164,19 +4161,19 @@
     </row>
     <row r="133" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F133" s="3">
         <v>5.9830780262751702E-2</v>
@@ -4190,19 +4187,19 @@
     </row>
     <row r="134" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F134" s="3">
         <v>0.14482314881505601</v>
@@ -4216,19 +4213,19 @@
     </row>
     <row r="135" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F135" s="3">
         <v>5.9830635009877099E-2</v>
@@ -4242,19 +4239,19 @@
     </row>
     <row r="136" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F136" s="3">
         <v>0.11299470313950701</v>
@@ -4268,19 +4265,19 @@
     </row>
     <row r="137" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F137" s="3">
         <v>5.0167904576220899</v>
@@ -4294,19 +4291,19 @@
     </row>
     <row r="138" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F138" s="3">
         <v>1.4815853247341099E-2</v>
@@ -4320,19 +4317,19 @@
     </row>
     <row r="139" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F139" s="3">
         <v>0.13447274880385601</v>
@@ -4346,19 +4343,19 @@
     </row>
     <row r="140" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F140" s="3">
         <v>9.8182415504397005E-2</v>
@@ -4372,19 +4369,19 @@
     </row>
     <row r="141" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F141" s="3">
         <v>1</v>
@@ -4398,19 +4395,19 @@
     </row>
     <row r="142" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F142" s="3">
         <v>2.0693118012869902E-3</v>
@@ -4424,25 +4421,25 @@
     </row>
     <row r="143" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C143" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D143" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D143" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E143" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F143" s="3">
         <v>1</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>0</v>
@@ -4450,25 +4447,25 @@
     </row>
     <row r="144" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B144" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D144" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C144" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E144" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F144" s="3">
         <v>1</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>0</v>
@@ -4476,25 +4473,25 @@
     </row>
     <row r="145" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F145" s="3">
         <v>1</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>0</v>
@@ -4502,10 +4499,10 @@
     </row>
     <row r="146" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>29</v>
@@ -4528,7 +4525,7 @@
     </row>
     <row r="147" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B147" s="2" t="s">
         <v>25</v>
@@ -4554,7 +4551,7 @@
     </row>
     <row r="148" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B148" s="2" t="s">
         <v>24</v>
@@ -4580,7 +4577,7 @@
     </row>
     <row r="149" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B149" s="2" t="s">
         <v>23</v>
@@ -4606,7 +4603,7 @@
     </row>
     <row r="150" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B150" s="2" t="s">
         <v>22</v>
@@ -4632,7 +4629,7 @@
     </row>
     <row r="151" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B151" s="2" t="s">
         <v>21</v>
@@ -4658,7 +4655,7 @@
     </row>
     <row r="152" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B152" s="2" t="s">
         <v>20</v>
@@ -4684,7 +4681,7 @@
     </row>
     <row r="153" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B153" s="2" t="s">
         <v>19</v>
@@ -4710,7 +4707,7 @@
     </row>
     <row r="154" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B154" s="2" t="s">
         <v>18</v>
@@ -4736,7 +4733,7 @@
     </row>
     <row r="155" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B155" s="2" t="s">
         <v>17</v>
@@ -4762,7 +4759,7 @@
     </row>
     <row r="156" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B156" s="2" t="s">
         <v>16</v>
@@ -4788,7 +4785,7 @@
     </row>
     <row r="157" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B157" s="2" t="s">
         <v>15</v>
@@ -4814,7 +4811,7 @@
     </row>
     <row r="158" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B158" s="2" t="s">
         <v>14</v>
@@ -4840,7 +4837,7 @@
     </row>
     <row r="159" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B159" s="2" t="s">
         <v>13</v>
@@ -4866,7 +4863,7 @@
     </row>
     <row r="160" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>12</v>
@@ -4892,7 +4889,7 @@
     </row>
     <row r="161" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>11</v>
@@ -4918,7 +4915,7 @@
     </row>
     <row r="162" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B162" s="2" t="s">
         <v>10</v>
@@ -4944,7 +4941,7 @@
     </row>
     <row r="163" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B163" s="2" t="s">
         <v>9</v>
@@ -4970,7 +4967,7 @@
     </row>
     <row r="164" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B164" s="2" t="s">
         <v>8</v>
@@ -4996,7 +4993,7 @@
     </row>
     <row r="165" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B165" s="2" t="s">
         <v>7</v>
@@ -5022,7 +5019,7 @@
     </row>
     <row r="166" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B166" s="2" t="s">
         <v>5</v>
@@ -5048,10 +5045,10 @@
     </row>
     <row r="167" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>4</v>
@@ -5074,10 +5071,10 @@
     </row>
     <row r="168" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>4</v>
@@ -5100,10 +5097,10 @@
     </row>
     <row r="169" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C169" s="2" t="s">
         <v>4</v>
@@ -5126,10 +5123,10 @@
     </row>
     <row r="170" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C170" s="2" t="s">
         <v>4</v>
@@ -5152,10 +5149,10 @@
     </row>
     <row r="171" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C171" s="2" t="s">
         <v>4</v>
@@ -5178,10 +5175,10 @@
     </row>
     <row r="172" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C172" s="2" t="s">
         <v>4</v>
@@ -5204,10 +5201,10 @@
     </row>
     <row r="173" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C173" s="2" t="s">
         <v>4</v>
@@ -5230,10 +5227,10 @@
     </row>
     <row r="174" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>4</v>
@@ -5256,10 +5253,10 @@
     </row>
     <row r="175" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>4</v>
@@ -5282,10 +5279,10 @@
     </row>
     <row r="176" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>4</v>
@@ -5308,10 +5305,10 @@
     </row>
     <row r="177" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>4</v>
@@ -5334,10 +5331,10 @@
     </row>
     <row r="178" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>4</v>
@@ -5360,10 +5357,10 @@
     </row>
     <row r="179" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>4</v>
@@ -5386,10 +5383,10 @@
     </row>
     <row r="180" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>4</v>
@@ -5412,19 +5409,19 @@
     </row>
     <row r="181" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F181" s="3">
         <v>2.0835026156931099E-3</v>
@@ -5438,19 +5435,19 @@
     </row>
     <row r="182" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F182" s="3">
         <v>1.25837693704109E-3</v>
@@ -5464,19 +5461,19 @@
     </row>
     <row r="183" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F183" s="3">
         <v>5.4268174427811199E-2</v>
@@ -5490,19 +5487,19 @@
     </row>
     <row r="184" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F184" s="3">
         <v>2.5830055170064599E-2</v>
@@ -5516,19 +5513,19 @@
     </row>
     <row r="185" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F185" s="3">
         <v>1.4909492702498899E-2</v>
@@ -5542,19 +5539,19 @@
     </row>
     <row r="186" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F186" s="3">
         <v>0.33893984045630199</v>
@@ -5568,19 +5565,19 @@
     </row>
     <row r="187" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F187" s="3">
         <v>0.13557079916214301</v>
@@ -5594,19 +5591,19 @@
     </row>
     <row r="188" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D188" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E188" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F188" s="3">
         <v>0.36520162524795502</v>
@@ -5620,19 +5617,19 @@
     </row>
     <row r="189" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D189" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E189" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F189" s="3">
         <v>0.32330915893409601</v>
@@ -5646,19 +5643,19 @@
     </row>
     <row r="190" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F190" s="3">
         <v>0.36520162524795502</v>
@@ -5672,19 +5669,19 @@
     </row>
     <row r="191" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F191" s="3">
         <v>0.25979498150225999</v>
@@ -5698,19 +5695,19 @@
     </row>
     <row r="192" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F192" s="3">
         <v>4.3920338967994503</v>
@@ -5724,19 +5721,19 @@
     </row>
     <row r="193" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F193" s="3">
         <v>0.21253205845623599</v>
@@ -5750,19 +5747,19 @@
     </row>
     <row r="194" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F194" s="3">
         <v>0.30087194298797798</v>
@@ -5776,19 +5773,19 @@
     </row>
     <row r="195" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F195" s="3">
         <v>1.6131115146856601</v>
@@ -5802,19 +5799,19 @@
     </row>
     <row r="196" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F196" s="3">
         <v>1</v>
@@ -5828,19 +5825,19 @@
     </row>
     <row r="197" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F197" s="3">
         <v>0.478939920314502</v>
@@ -5854,25 +5851,25 @@
     </row>
     <row r="198" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C198" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D198" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D198" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E198" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F198" s="3">
         <v>1</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>0</v>
@@ -5880,25 +5877,25 @@
     </row>
     <row r="199" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B199" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D199" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C199" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D199" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E199" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F199" s="3">
         <v>1</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>0</v>
@@ -5906,25 +5903,25 @@
     </row>
     <row r="200" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D200" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E200" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F200" s="3">
         <v>1</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>0</v>
@@ -5932,10 +5929,10 @@
     </row>
     <row r="201" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C201" s="2" t="s">
         <v>29</v>
@@ -5958,7 +5955,7 @@
     </row>
     <row r="202" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>25</v>
@@ -5984,7 +5981,7 @@
     </row>
     <row r="203" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>24</v>
@@ -6010,7 +6007,7 @@
     </row>
     <row r="204" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>23</v>
@@ -6036,7 +6033,7 @@
     </row>
     <row r="205" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>22</v>
@@ -6062,7 +6059,7 @@
     </row>
     <row r="206" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>21</v>
@@ -6088,7 +6085,7 @@
     </row>
     <row r="207" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>20</v>
@@ -6114,7 +6111,7 @@
     </row>
     <row r="208" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>19</v>
@@ -6140,7 +6137,7 @@
     </row>
     <row r="209" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>18</v>
@@ -6166,7 +6163,7 @@
     </row>
     <row r="210" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>17</v>
@@ -6192,7 +6189,7 @@
     </row>
     <row r="211" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>16</v>
@@ -6218,7 +6215,7 @@
     </row>
     <row r="212" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>15</v>
@@ -6244,7 +6241,7 @@
     </row>
     <row r="213" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>14</v>
@@ -6270,7 +6267,7 @@
     </row>
     <row r="214" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>13</v>
@@ -6296,7 +6293,7 @@
     </row>
     <row r="215" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>12</v>
@@ -6322,7 +6319,7 @@
     </row>
     <row r="216" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>11</v>
@@ -6348,7 +6345,7 @@
     </row>
     <row r="217" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>10</v>
@@ -6374,7 +6371,7 @@
     </row>
     <row r="218" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>9</v>
@@ -6400,7 +6397,7 @@
     </row>
     <row r="219" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>8</v>
@@ -6426,7 +6423,7 @@
     </row>
     <row r="220" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>7</v>
@@ -6452,7 +6449,7 @@
     </row>
     <row r="221" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>5</v>
@@ -6478,10 +6475,10 @@
     </row>
     <row r="222" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C222" s="2" t="s">
         <v>4</v>
@@ -6504,10 +6501,10 @@
     </row>
     <row r="223" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C223" s="2" t="s">
         <v>4</v>
@@ -6530,10 +6527,10 @@
     </row>
     <row r="224" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C224" s="2" t="s">
         <v>4</v>
@@ -6556,10 +6553,10 @@
     </row>
     <row r="225" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>4</v>
@@ -6582,10 +6579,10 @@
     </row>
     <row r="226" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>4</v>
@@ -6608,10 +6605,10 @@
     </row>
     <row r="227" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C227" s="2" t="s">
         <v>4</v>
@@ -6634,10 +6631,10 @@
     </row>
     <row r="228" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>4</v>
@@ -6660,10 +6657,10 @@
     </row>
     <row r="229" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C229" s="2" t="s">
         <v>4</v>
@@ -6686,10 +6683,10 @@
     </row>
     <row r="230" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>4</v>
@@ -6712,10 +6709,10 @@
     </row>
     <row r="231" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>4</v>
@@ -6738,10 +6735,10 @@
     </row>
     <row r="232" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>4</v>
@@ -6764,10 +6761,10 @@
     </row>
     <row r="233" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C233" s="2" t="s">
         <v>4</v>
@@ -6790,10 +6787,10 @@
     </row>
     <row r="234" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C234" s="2" t="s">
         <v>4</v>
@@ -6816,10 +6813,10 @@
     </row>
     <row r="235" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C235" s="2" t="s">
         <v>4</v>
@@ -6842,19 +6839,19 @@
     </row>
     <row r="236" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D236" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E236" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F236" s="3">
         <v>2.4161916393854498E-3</v>
@@ -6868,19 +6865,19 @@
     </row>
     <row r="237" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F237" s="3">
         <v>1.48668913034362E-3</v>
@@ -6894,19 +6891,19 @@
     </row>
     <row r="238" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F238" s="3">
         <v>6.1936380007275603E-2</v>
@@ -6920,19 +6917,19 @@
     </row>
     <row r="239" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F239" s="3">
         <v>2.73408717083557E-2</v>
@@ -6946,19 +6943,19 @@
     </row>
     <row r="240" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F240" s="3">
         <v>1.47769922971181E-2</v>
@@ -6972,19 +6969,19 @@
     </row>
     <row r="241" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F241" s="3">
         <v>0.42507894219752301</v>
@@ -6998,19 +6995,19 @@
     </row>
     <row r="242" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F242" s="3">
         <v>0.14523287887126399</v>
@@ -7024,19 +7021,19 @@
     </row>
     <row r="243" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F243" s="3">
         <v>0.46806313379755599</v>
@@ -7050,19 +7047,19 @@
     </row>
     <row r="244" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F244" s="3">
         <v>0.39379516643275497</v>
@@ -7076,19 +7073,19 @@
     </row>
     <row r="245" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F245" s="3">
         <v>0.46806313379755599</v>
@@ -7102,19 +7099,19 @@
     </row>
     <row r="246" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F246" s="3">
         <v>0.30411078297932698</v>
@@ -7128,19 +7125,19 @@
     </row>
     <row r="247" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F247" s="3">
         <v>5.4569848567658799</v>
@@ -7154,19 +7151,19 @@
     </row>
     <row r="248" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F248" s="3">
         <v>0.22835961046438499</v>
@@ -7180,19 +7177,19 @@
     </row>
     <row r="249" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F249" s="3">
         <v>0.36348274030883498</v>
@@ -7206,19 +7203,19 @@
     </row>
     <row r="250" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F250" s="3">
         <v>1.6428638520182901</v>
@@ -7232,19 +7229,19 @@
     </row>
     <row r="251" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F251" s="3">
         <v>1</v>
@@ -7258,19 +7255,19 @@
     </row>
     <row r="252" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F252" s="3">
         <v>0.432291367462034</v>
@@ -7284,25 +7281,25 @@
     </row>
     <row r="253" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C253" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D253" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D253" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E253" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F253" s="3">
         <v>1</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>0</v>
@@ -7310,25 +7307,25 @@
     </row>
     <row r="254" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B254" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D254" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C254" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D254" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E254" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F254" s="3">
         <v>1</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>0</v>
@@ -7336,25 +7333,25 @@
     </row>
     <row r="255" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F255" s="3">
         <v>1</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>0</v>
@@ -7362,10 +7359,10 @@
     </row>
     <row r="256" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>29</v>
@@ -7388,7 +7385,7 @@
     </row>
     <row r="257" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>25</v>
@@ -7414,7 +7411,7 @@
     </row>
     <row r="258" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>24</v>
@@ -7440,7 +7437,7 @@
     </row>
     <row r="259" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>23</v>
@@ -7466,7 +7463,7 @@
     </row>
     <row r="260" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>22</v>
@@ -7492,7 +7489,7 @@
     </row>
     <row r="261" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>21</v>
@@ -7518,7 +7515,7 @@
     </row>
     <row r="262" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>20</v>
@@ -7544,7 +7541,7 @@
     </row>
     <row r="263" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>19</v>
@@ -7570,7 +7567,7 @@
     </row>
     <row r="264" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>18</v>
@@ -7596,7 +7593,7 @@
     </row>
     <row r="265" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>17</v>
@@ -7622,7 +7619,7 @@
     </row>
     <row r="266" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>16</v>
@@ -7648,7 +7645,7 @@
     </row>
     <row r="267" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>15</v>
@@ -7674,7 +7671,7 @@
     </row>
     <row r="268" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>14</v>
@@ -7700,7 +7697,7 @@
     </row>
     <row r="269" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>13</v>
@@ -7726,7 +7723,7 @@
     </row>
     <row r="270" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>12</v>
@@ -7752,7 +7749,7 @@
     </row>
     <row r="271" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>11</v>
@@ -7778,7 +7775,7 @@
     </row>
     <row r="272" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>10</v>
@@ -7804,7 +7801,7 @@
     </row>
     <row r="273" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>9</v>
@@ -7830,7 +7827,7 @@
     </row>
     <row r="274" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>8</v>
@@ -7856,7 +7853,7 @@
     </row>
     <row r="275" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>7</v>
@@ -7882,7 +7879,7 @@
     </row>
     <row r="276" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>5</v>
@@ -7908,10 +7905,10 @@
     </row>
     <row r="277" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>4</v>
@@ -7934,10 +7931,10 @@
     </row>
     <row r="278" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>4</v>
@@ -7960,10 +7957,10 @@
     </row>
     <row r="279" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>4</v>
@@ -7986,10 +7983,10 @@
     </row>
     <row r="280" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>4</v>
@@ -8012,10 +8009,10 @@
     </row>
     <row r="281" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C281" s="2" t="s">
         <v>4</v>
@@ -8038,10 +8035,10 @@
     </row>
     <row r="282" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>4</v>
@@ -8064,10 +8061,10 @@
     </row>
     <row r="283" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>4</v>
@@ -8090,10 +8087,10 @@
     </row>
     <row r="284" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>4</v>
@@ -8116,10 +8113,10 @@
     </row>
     <row r="285" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>4</v>
@@ -8142,10 +8139,10 @@
     </row>
     <row r="286" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>4</v>
@@ -8168,10 +8165,10 @@
     </row>
     <row r="287" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>4</v>
@@ -8194,10 +8191,10 @@
     </row>
     <row r="288" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>4</v>
@@ -8220,10 +8217,10 @@
     </row>
     <row r="289" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>4</v>
@@ -8246,10 +8243,10 @@
     </row>
     <row r="290" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>4</v>
@@ -8272,19 +8269,19 @@
     </row>
     <row r="291" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F291" s="3">
         <v>1.9022677716969E-3</v>
@@ -8298,19 +8295,19 @@
     </row>
     <row r="292" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F292" s="3">
         <v>1.10938482115972E-3</v>
@@ -8324,19 +8321,19 @@
     </row>
     <row r="293" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F293" s="3">
         <v>4.9634377357630599E-2</v>
@@ -8350,19 +8347,19 @@
     </row>
     <row r="294" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F294" s="3">
         <v>2.4185866314721399E-2</v>
@@ -8376,19 +8373,19 @@
     </row>
     <row r="295" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F295" s="3">
         <v>1.4360439033987499E-2</v>
@@ -8402,19 +8399,19 @@
     </row>
     <row r="296" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F296" s="3">
         <v>0.28727914120621301</v>
@@ -8428,19 +8425,19 @@
     </row>
     <row r="297" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F297" s="3">
         <v>0.124847158301095</v>
@@ -8454,19 +8451,19 @@
     </row>
     <row r="298" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F298" s="3">
         <v>0.304313903456151</v>
@@ -8480,19 +8477,19 @@
     </row>
     <row r="299" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F299" s="3">
         <v>0.27717834277124898</v>
@@ -8506,19 +8503,19 @@
     </row>
     <row r="300" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F300" s="3">
         <v>0.304313903456151</v>
@@ -8532,19 +8529,19 @@
     </row>
     <row r="301" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F301" s="3">
         <v>0.228155904868315</v>
@@ -8558,19 +8555,19 @@
     </row>
     <row r="302" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F302" s="3">
         <v>3.7924076400235802</v>
@@ -8584,19 +8581,19 @@
     </row>
     <row r="303" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F303" s="3">
         <v>0.195619549105777</v>
@@ -8610,19 +8607,19 @@
     </row>
     <row r="304" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F304" s="3">
         <v>0.25902911011179902</v>
@@ -8636,19 +8633,19 @@
     </row>
     <row r="305" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F305" s="3">
         <v>1.51426556386306</v>
@@ -8662,19 +8659,19 @@
     </row>
     <row r="306" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F306" s="3">
         <v>1</v>
@@ -8688,19 +8685,19 @@
     </row>
     <row r="307" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F307" s="3">
         <v>0.470688702560144</v>
@@ -8714,25 +8711,25 @@
     </row>
     <row r="308" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C308" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D308" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D308" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E308" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F308" s="3">
         <v>1</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>0</v>
@@ -8740,25 +8737,25 @@
     </row>
     <row r="309" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B309" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D309" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C309" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D309" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E309" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F309" s="3">
         <v>1</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>0</v>
@@ -8766,25 +8763,25 @@
     </row>
     <row r="310" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F310" s="3">
         <v>1</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>0</v>
@@ -8792,10 +8789,10 @@
     </row>
     <row r="311" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>29</v>
@@ -8818,7 +8815,7 @@
     </row>
     <row r="312" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>25</v>
@@ -8844,7 +8841,7 @@
     </row>
     <row r="313" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>24</v>
@@ -8870,7 +8867,7 @@
     </row>
     <row r="314" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>23</v>
@@ -8896,7 +8893,7 @@
     </row>
     <row r="315" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>22</v>
@@ -8922,7 +8919,7 @@
     </row>
     <row r="316" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>21</v>
@@ -8948,7 +8945,7 @@
     </row>
     <row r="317" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>20</v>
@@ -8974,7 +8971,7 @@
     </row>
     <row r="318" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>19</v>
@@ -9000,7 +8997,7 @@
     </row>
     <row r="319" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>18</v>
@@ -9026,7 +9023,7 @@
     </row>
     <row r="320" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>17</v>
@@ -9052,7 +9049,7 @@
     </row>
     <row r="321" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>16</v>
@@ -9078,7 +9075,7 @@
     </row>
     <row r="322" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>15</v>
@@ -9104,7 +9101,7 @@
     </row>
     <row r="323" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>14</v>
@@ -9130,7 +9127,7 @@
     </row>
     <row r="324" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>13</v>
@@ -9156,7 +9153,7 @@
     </row>
     <row r="325" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>12</v>
@@ -9182,7 +9179,7 @@
     </row>
     <row r="326" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>11</v>
@@ -9208,7 +9205,7 @@
     </row>
     <row r="327" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>10</v>
@@ -9234,7 +9231,7 @@
     </row>
     <row r="328" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>9</v>
@@ -9260,7 +9257,7 @@
     </row>
     <row r="329" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>8</v>
@@ -9286,7 +9283,7 @@
     </row>
     <row r="330" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>7</v>
@@ -9312,7 +9309,7 @@
     </row>
     <row r="331" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>5</v>
@@ -9338,10 +9335,10 @@
     </row>
     <row r="332" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>4</v>
@@ -9364,10 +9361,10 @@
     </row>
     <row r="333" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>4</v>
@@ -9390,10 +9387,10 @@
     </row>
     <row r="334" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>4</v>
@@ -9416,10 +9413,10 @@
     </row>
     <row r="335" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C335" s="2" t="s">
         <v>4</v>
@@ -9442,10 +9439,10 @@
     </row>
     <row r="336" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>4</v>
@@ -9468,10 +9465,10 @@
     </row>
     <row r="337" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>4</v>
@@ -9494,10 +9491,10 @@
     </row>
     <row r="338" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>4</v>
@@ -9520,10 +9517,10 @@
     </row>
     <row r="339" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>4</v>
@@ -9546,10 +9543,10 @@
     </row>
     <row r="340" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>4</v>
@@ -9572,10 +9569,10 @@
     </row>
     <row r="341" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>4</v>
@@ -9598,10 +9595,10 @@
     </row>
     <row r="342" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C342" s="2" t="s">
         <v>4</v>
@@ -9624,10 +9621,10 @@
     </row>
     <row r="343" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>4</v>
@@ -9650,10 +9647,10 @@
     </row>
     <row r="344" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>4</v>
@@ -9676,10 +9673,10 @@
     </row>
     <row r="345" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C345" s="2" t="s">
         <v>4</v>
@@ -9702,19 +9699,19 @@
     </row>
     <row r="346" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D346" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E346" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F346" s="3">
         <v>1.6640042799492599E-3</v>
@@ -9728,19 +9725,19 @@
     </row>
     <row r="347" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D347" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E347" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F347" s="3">
         <v>1.0224835460863799E-3</v>
@@ -9754,19 +9751,19 @@
     </row>
     <row r="348" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D348" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E348" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F348" s="3">
         <v>4.4496549952477198E-2</v>
@@ -9780,19 +9777,19 @@
     </row>
     <row r="349" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D349" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E349" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F349" s="3">
         <v>2.31594414459677E-2</v>
@@ -9806,19 +9803,19 @@
     </row>
     <row r="350" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D350" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E350" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F350" s="3">
         <v>1.41052720167524E-2</v>
@@ -9832,19 +9829,19 @@
     </row>
     <row r="351" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D351" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E351" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F351" s="3">
         <v>0.263983123286745</v>
@@ -9858,19 +9855,19 @@
     </row>
     <row r="352" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D352" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E352" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F352" s="3">
         <v>0.12259834669969299</v>
@@ -9884,19 +9881,19 @@
     </row>
     <row r="353" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D353" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E353" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F353" s="3">
         <v>0.279694678479457</v>
@@ -9910,19 +9907,19 @@
     </row>
     <row r="354" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D354" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E354" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F354" s="3">
         <v>0.25987126009719502</v>
@@ -9936,19 +9933,19 @@
     </row>
     <row r="355" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D355" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E355" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F355" s="3">
         <v>0.279694678479457</v>
@@ -9962,19 +9959,19 @@
     </row>
     <row r="356" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D356" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E356" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F356" s="3">
         <v>0.21671852410480399</v>
@@ -9988,19 +9985,19 @@
     </row>
     <row r="357" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D357" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E357" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F357" s="3">
         <v>3.3406217911408498</v>
@@ -10014,19 +10011,19 @@
     </row>
     <row r="358" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D358" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E358" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F358" s="3">
         <v>0.18628869379590701</v>
@@ -10040,19 +10037,19 @@
     </row>
     <row r="359" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D359" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E359" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F359" s="3">
         <v>0.244488226709585</v>
@@ -10066,19 +10063,19 @@
     </row>
     <row r="360" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D360" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E360" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F360" s="3">
         <v>1.4599462355708701</v>
@@ -10092,19 +10089,19 @@
     </row>
     <row r="361" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D361" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E361" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F361" s="3">
         <v>1</v>
@@ -10118,19 +10115,19 @@
     </row>
     <row r="362" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D362" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E362" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F362" s="3">
         <v>0.46957320605790798</v>
@@ -10144,25 +10141,25 @@
     </row>
     <row r="363" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C363" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D363" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D363" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E363" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F363" s="3">
         <v>1</v>
       </c>
       <c r="G363" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H363" s="2" t="s">
         <v>0</v>
@@ -10170,25 +10167,25 @@
     </row>
     <row r="364" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B364" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D364" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C364" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D364" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E364" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F364" s="3">
         <v>1</v>
       </c>
       <c r="G364" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H364" s="2" t="s">
         <v>0</v>
@@ -10196,25 +10193,25 @@
     </row>
     <row r="365" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D365" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E365" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F365" s="3">
         <v>1</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H365" s="2" t="s">
         <v>0</v>
@@ -10222,10 +10219,10 @@
     </row>
     <row r="366" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C366" s="2" t="s">
         <v>29</v>
@@ -10248,7 +10245,7 @@
     </row>
     <row r="367" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B367" s="2" t="s">
         <v>25</v>
@@ -10274,7 +10271,7 @@
     </row>
     <row r="368" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B368" s="2" t="s">
         <v>24</v>
@@ -10300,7 +10297,7 @@
     </row>
     <row r="369" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B369" s="2" t="s">
         <v>23</v>
@@ -10326,7 +10323,7 @@
     </row>
     <row r="370" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B370" s="2" t="s">
         <v>22</v>
@@ -10352,7 +10349,7 @@
     </row>
     <row r="371" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B371" s="2" t="s">
         <v>21</v>
@@ -10378,7 +10375,7 @@
     </row>
     <row r="372" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B372" s="2" t="s">
         <v>20</v>
@@ -10404,7 +10401,7 @@
     </row>
     <row r="373" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B373" s="2" t="s">
         <v>19</v>
@@ -10430,7 +10427,7 @@
     </row>
     <row r="374" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B374" s="2" t="s">
         <v>18</v>
@@ -10456,7 +10453,7 @@
     </row>
     <row r="375" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B375" s="2" t="s">
         <v>17</v>
@@ -10482,7 +10479,7 @@
     </row>
     <row r="376" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B376" s="2" t="s">
         <v>16</v>
@@ -10508,7 +10505,7 @@
     </row>
     <row r="377" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B377" s="2" t="s">
         <v>15</v>
@@ -10534,7 +10531,7 @@
     </row>
     <row r="378" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B378" s="2" t="s">
         <v>14</v>
@@ -10560,7 +10557,7 @@
     </row>
     <row r="379" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B379" s="2" t="s">
         <v>13</v>
@@ -10586,7 +10583,7 @@
     </row>
     <row r="380" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B380" s="2" t="s">
         <v>12</v>
@@ -10612,7 +10609,7 @@
     </row>
     <row r="381" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B381" s="2" t="s">
         <v>11</v>
@@ -10638,7 +10635,7 @@
     </row>
     <row r="382" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B382" s="2" t="s">
         <v>10</v>
@@ -10664,7 +10661,7 @@
     </row>
     <row r="383" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B383" s="2" t="s">
         <v>9</v>
@@ -10690,7 +10687,7 @@
     </row>
     <row r="384" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B384" s="2" t="s">
         <v>8</v>
@@ -10716,7 +10713,7 @@
     </row>
     <row r="385" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B385" s="2" t="s">
         <v>7</v>
@@ -10742,7 +10739,7 @@
     </row>
     <row r="386" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B386" s="2" t="s">
         <v>5</v>
@@ -10768,10 +10765,10 @@
     </row>
     <row r="387" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C387" s="2" t="s">
         <v>4</v>
@@ -10794,10 +10791,10 @@
     </row>
     <row r="388" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C388" s="2" t="s">
         <v>4</v>
@@ -10820,10 +10817,10 @@
     </row>
     <row r="389" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C389" s="2" t="s">
         <v>4</v>
@@ -10846,10 +10843,10 @@
     </row>
     <row r="390" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C390" s="2" t="s">
         <v>4</v>
@@ -10872,10 +10869,10 @@
     </row>
     <row r="391" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B391" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C391" s="2" t="s">
         <v>4</v>
@@ -10898,10 +10895,10 @@
     </row>
     <row r="392" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B392" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C392" s="2" t="s">
         <v>4</v>
@@ -10924,10 +10921,10 @@
     </row>
     <row r="393" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B393" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C393" s="2" t="s">
         <v>4</v>
@@ -10950,10 +10947,10 @@
     </row>
     <row r="394" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B394" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C394" s="2" t="s">
         <v>4</v>
@@ -10976,10 +10973,10 @@
     </row>
     <row r="395" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B395" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C395" s="2" t="s">
         <v>4</v>
@@ -11002,10 +10999,10 @@
     </row>
     <row r="396" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B396" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C396" s="2" t="s">
         <v>4</v>
@@ -11028,10 +11025,10 @@
     </row>
     <row r="397" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B397" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C397" s="2" t="s">
         <v>4</v>
@@ -11054,10 +11051,10 @@
     </row>
     <row r="398" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B398" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C398" s="2" t="s">
         <v>4</v>
@@ -11080,10 +11077,10 @@
     </row>
     <row r="399" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B399" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C399" s="2" t="s">
         <v>4</v>
@@ -11106,10 +11103,10 @@
     </row>
     <row r="400" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B400" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C400" s="2" t="s">
         <v>4</v>
@@ -11132,19 +11129,19 @@
     </row>
     <row r="401" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B401" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C401" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D401" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E401" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F401" s="3">
         <v>2.2334916117283101E-3</v>
@@ -11158,19 +11155,19 @@
     </row>
     <row r="402" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B402" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C402" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D402" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E402" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F402" s="3">
         <v>1.36396756539204E-3</v>
@@ -11184,19 +11181,19 @@
     </row>
     <row r="403" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B403" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C403" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D403" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E403" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F403" s="3">
         <v>5.7942193200197299E-2</v>
@@ -11210,19 +11207,19 @@
     </row>
     <row r="404" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B404" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C404" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D404" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E404" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F404" s="3">
         <v>2.7012176958968799E-2</v>
@@ -11236,19 +11233,19 @@
     </row>
     <row r="405" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B405" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C405" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D405" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E405" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F405" s="3">
         <v>1.52757286834862E-2</v>
@@ -11262,19 +11259,19 @@
     </row>
     <row r="406" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B406" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C406" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D406" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E406" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F406" s="3">
         <v>0.374829216964567</v>
@@ -11288,19 +11285,19 @@
     </row>
     <row r="407" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B407" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C407" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D407" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E407" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F407" s="3">
         <v>0.14247052509799901</v>
@@ -11314,19 +11311,19 @@
     </row>
     <row r="408" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B408" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C408" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D408" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E408" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F408" s="3">
         <v>0.40725427766495098</v>
@@ -11340,19 +11337,19 @@
     </row>
     <row r="409" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B409" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C409" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D409" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E409" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F409" s="3">
         <v>0.35462192706434098</v>
@@ -11366,19 +11363,19 @@
     </row>
     <row r="410" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B410" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C410" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D410" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E410" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F410" s="3">
         <v>0.40725427766495098</v>
@@ -11392,19 +11389,19 @@
     </row>
     <row r="411" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B411" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C411" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D411" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E411" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F411" s="3">
         <v>0.28114525755665798</v>
@@ -11418,19 +11415,19 @@
     </row>
     <row r="412" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B412" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C412" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D412" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E412" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F412" s="3">
         <v>4.8307283756980004</v>
@@ -11444,19 +11441,19 @@
     </row>
     <row r="413" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B413" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C413" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D413" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E413" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F413" s="3">
         <v>0.22359854726456099</v>
@@ -11470,19 +11467,19 @@
     </row>
     <row r="414" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B414" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C414" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D414" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E414" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F414" s="3">
         <v>0.32914096146635302</v>
@@ -11496,19 +11493,19 @@
     </row>
     <row r="415" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B415" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C415" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D415" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E415" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F415" s="3">
         <v>1.66997848562103</v>
@@ -11522,19 +11519,19 @@
     </row>
     <row r="416" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B416" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C416" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D416" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E416" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F416" s="3">
         <v>1</v>
@@ -11548,19 +11545,19 @@
     </row>
     <row r="417" spans="1:8" ht="105" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B417" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C417" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D417" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E417" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F417" s="3">
         <v>0.47498285068043999</v>
@@ -11574,25 +11571,25 @@
     </row>
     <row r="418" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B418" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C418" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D418" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D418" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E418" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F418" s="3">
         <v>1</v>
       </c>
       <c r="G418" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H418" s="2" t="s">
         <v>0</v>
@@ -11600,25 +11597,25 @@
     </row>
     <row r="419" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B419" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C419" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D419" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C419" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D419" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E419" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F419" s="3">
         <v>1</v>
       </c>
       <c r="G419" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H419" s="2" t="s">
         <v>0</v>
@@ -11626,25 +11623,25 @@
     </row>
     <row r="420" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B420" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C420" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D420" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E420" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F420" s="3">
         <v>1</v>
       </c>
       <c r="G420" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H420" s="2" t="s">
         <v>0</v>
@@ -11652,10 +11649,10 @@
     </row>
     <row r="421" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B421" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C421" s="2" t="s">
         <v>29</v>
@@ -11678,7 +11675,7 @@
     </row>
     <row r="422" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B422" s="2" t="s">
         <v>25</v>
@@ -11704,7 +11701,7 @@
     </row>
     <row r="423" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B423" s="2" t="s">
         <v>24</v>
@@ -11730,7 +11727,7 @@
     </row>
     <row r="424" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B424" s="2" t="s">
         <v>23</v>
@@ -11756,7 +11753,7 @@
     </row>
     <row r="425" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B425" s="2" t="s">
         <v>22</v>
@@ -11782,7 +11779,7 @@
     </row>
     <row r="426" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B426" s="2" t="s">
         <v>21</v>
@@ -11808,7 +11805,7 @@
     </row>
     <row r="427" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B427" s="2" t="s">
         <v>20</v>
@@ -11834,7 +11831,7 @@
     </row>
     <row r="428" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B428" s="2" t="s">
         <v>19</v>
@@ -11860,7 +11857,7 @@
     </row>
     <row r="429" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B429" s="2" t="s">
         <v>18</v>
@@ -11886,7 +11883,7 @@
     </row>
     <row r="430" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B430" s="2" t="s">
         <v>17</v>
@@ -11912,7 +11909,7 @@
     </row>
     <row r="431" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B431" s="2" t="s">
         <v>16</v>
@@ -11938,7 +11935,7 @@
     </row>
     <row r="432" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B432" s="2" t="s">
         <v>15</v>
@@ -11964,7 +11961,7 @@
     </row>
     <row r="433" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B433" s="2" t="s">
         <v>14</v>
@@ -11990,7 +11987,7 @@
     </row>
     <row r="434" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B434" s="2" t="s">
         <v>13</v>
@@ -12016,7 +12013,7 @@
     </row>
     <row r="435" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B435" s="2" t="s">
         <v>12</v>
@@ -12042,7 +12039,7 @@
     </row>
     <row r="436" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B436" s="2" t="s">
         <v>11</v>
@@ -12068,7 +12065,7 @@
     </row>
     <row r="437" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B437" s="2" t="s">
         <v>10</v>
@@ -12094,7 +12091,7 @@
     </row>
     <row r="438" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B438" s="2" t="s">
         <v>9</v>
@@ -12120,7 +12117,7 @@
     </row>
     <row r="439" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B439" s="2" t="s">
         <v>8</v>
@@ -12146,7 +12143,7 @@
     </row>
     <row r="440" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B440" s="2" t="s">
         <v>7</v>
@@ -12172,7 +12169,7 @@
     </row>
     <row r="441" spans="1:8" ht="75" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B441" s="2" t="s">
         <v>5</v>
@@ -12201,7 +12198,7 @@
         <v>6</v>
       </c>
       <c r="B442" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C442" s="2" t="s">
         <v>4</v>
@@ -12227,7 +12224,7 @@
         <v>6</v>
       </c>
       <c r="B443" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C443" s="2" t="s">
         <v>4</v>
@@ -12253,7 +12250,7 @@
         <v>6</v>
       </c>
       <c r="B444" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C444" s="2" t="s">
         <v>4</v>
@@ -12279,7 +12276,7 @@
         <v>6</v>
       </c>
       <c r="B445" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C445" s="2" t="s">
         <v>4</v>
@@ -12305,7 +12302,7 @@
         <v>6</v>
       </c>
       <c r="B446" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C446" s="2" t="s">
         <v>4</v>
@@ -12331,7 +12328,7 @@
         <v>6</v>
       </c>
       <c r="B447" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C447" s="2" t="s">
         <v>4</v>
@@ -12357,7 +12354,7 @@
         <v>6</v>
       </c>
       <c r="B448" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C448" s="2" t="s">
         <v>4</v>
@@ -12383,7 +12380,7 @@
         <v>6</v>
       </c>
       <c r="B449" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C449" s="2" t="s">
         <v>4</v>
@@ -12409,7 +12406,7 @@
         <v>6</v>
       </c>
       <c r="B450" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C450" s="2" t="s">
         <v>4</v>
@@ -12435,7 +12432,7 @@
         <v>6</v>
       </c>
       <c r="B451" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C451" s="2" t="s">
         <v>4</v>
@@ -12461,7 +12458,7 @@
         <v>6</v>
       </c>
       <c r="B452" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C452" s="2" t="s">
         <v>4</v>
@@ -12487,7 +12484,7 @@
         <v>6</v>
       </c>
       <c r="B453" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C453" s="2" t="s">
         <v>4</v>
@@ -12513,7 +12510,7 @@
         <v>6</v>
       </c>
       <c r="B454" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C454" s="2" t="s">
         <v>4</v>
@@ -12539,7 +12536,7 @@
         <v>6</v>
       </c>
       <c r="B455" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C455" s="2" t="s">
         <v>4</v>
@@ -12565,16 +12562,16 @@
         <v>6</v>
       </c>
       <c r="B456" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C456" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D456" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E456" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F456" s="3">
         <v>2.81507284519193E-4</v>
@@ -12591,16 +12588,16 @@
         <v>6</v>
       </c>
       <c r="B457" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C457" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D457" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E457" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F457" s="3">
         <v>1.5233158493349901E-4</v>
@@ -12617,16 +12614,16 @@
         <v>6</v>
       </c>
       <c r="B458" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C458" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D458" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E458" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F458" s="3">
         <v>9.4151416015945903E-3</v>
@@ -12643,16 +12640,16 @@
         <v>6</v>
       </c>
       <c r="B459" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C459" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D459" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E459" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F459" s="3">
         <v>9.2435710964990994E-3</v>
@@ -12669,16 +12666,16 @@
         <v>6</v>
       </c>
       <c r="B460" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C460" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D460" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E460" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F460" s="3">
         <v>5.5026308309961197E-3</v>
@@ -12695,16 +12692,16 @@
         <v>6</v>
       </c>
       <c r="B461" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C461" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D461" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E461" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F461" s="3">
         <v>2.2217671575165001</v>
@@ -12721,16 +12718,16 @@
         <v>6</v>
       </c>
       <c r="B462" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C462" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D462" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E462" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F462" s="3">
         <v>4.9948191128881901E-2</v>
@@ -12747,16 +12744,16 @@
         <v>6</v>
       </c>
       <c r="B463" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C463" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D463" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E463" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F463" s="3">
         <v>4.8047584470129898E-2</v>
@@ -12773,16 +12770,16 @@
         <v>6</v>
       </c>
       <c r="B464" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C464" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D464" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E464" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F464" s="3">
         <v>0.117351143507426</v>
@@ -12799,16 +12796,16 @@
         <v>6</v>
       </c>
       <c r="B465" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C465" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D465" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E465" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F465" s="3">
         <v>4.8047554149726397E-2</v>
@@ -12825,16 +12822,16 @@
         <v>6</v>
       </c>
       <c r="B466" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C466" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D466" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E466" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F466" s="3">
         <v>9.3646393741823694E-2</v>
@@ -12851,16 +12848,16 @@
         <v>6</v>
       </c>
       <c r="B467" s="2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C467" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D467" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E467" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F467" s="3">
         <v>4.33602424484413</v>
@@ -12877,16 +12874,16 @@
         <v>6</v>
       </c>
       <c r="B468" s="2" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C468" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D468" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E468" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F468" s="3">
         <v>1.4864937770859499E-2</v>
@@ -12903,16 +12900,16 @@
         <v>6</v>
       </c>
       <c r="B469" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C469" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D469" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E469" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F469" s="3">
         <v>0.108965827319639</v>
@@ -12929,16 +12926,16 @@
         <v>6</v>
       </c>
       <c r="B470" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C470" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D470" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E470" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F470" s="3">
         <v>0.11797744143090901</v>
@@ -12955,16 +12952,16 @@
         <v>6</v>
       </c>
       <c r="B471" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C471" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D471" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E471" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F471" s="3">
         <v>1</v>
@@ -12981,16 +12978,16 @@
         <v>6</v>
       </c>
       <c r="B472" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C472" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D472" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E472" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F472" s="3">
         <v>3.7539083517887802E-3</v>
@@ -13007,22 +13004,22 @@
         <v>6</v>
       </c>
       <c r="B473" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C473" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D473" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D473" s="2" t="s">
-        <v>37</v>
-      </c>
       <c r="E473" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F473" s="3">
         <v>1</v>
       </c>
       <c r="G473" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H473" s="2" t="s">
         <v>0</v>
@@ -13033,22 +13030,22 @@
         <v>6</v>
       </c>
       <c r="B474" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C474" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D474" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C474" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D474" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="E474" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F474" s="3">
         <v>1</v>
       </c>
       <c r="G474" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H474" s="2" t="s">
         <v>0</v>
@@ -13059,22 +13056,22 @@
         <v>6</v>
       </c>
       <c r="B475" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C475" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D475" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E475" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F475" s="3">
         <v>1</v>
       </c>
       <c r="G475" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H475" s="2" t="s">
         <v>0</v>
@@ -13085,7 +13082,7 @@
         <v>6</v>
       </c>
       <c r="B476" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C476" s="2" t="s">
         <v>29</v>
@@ -13627,6 +13624,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H1" xr:uid="{6B985253-29BF-49D3-99D7-AF537F574A8C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>